--- a/artfynd/A 39996-2025 artfynd.xlsx
+++ b/artfynd/A 39996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133056788</v>
+        <v>132638990</v>
       </c>
       <c r="B2" t="n">
-        <v>96368</v>
+        <v>96030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>2381</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Bandpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Plagiomnium elatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnetjärnet Vut 5, Dls</t>
+          <t>Kilevass, ca 950 m NNO om. Östvänd bergbrant ca 300 m V om Kvarnetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337120</v>
+        <v>337203</v>
       </c>
       <c r="R2" t="n">
-        <v>6524546</v>
+        <v>6524686</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,19 +756,1177 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Östvänd bergvägg vid smal myr  i skog.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Sten, lodyta.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133054808</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96030</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2381</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bandpraktmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Plagiomnium elatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bruch &amp; Schimp.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kvarnetjärnet Vut 4, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>337186</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6524666</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Niklas Lönnell</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Niklas Lönnell, Leif Appelgren</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133056776</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96106</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2558</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Krushättemossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kvarnetjärnet Vut 5, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>337120</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6524546</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell, Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133132832</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97889</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2605</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stenporella</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porella cordaeana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Huebener) Moore</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kilevass, ca 950 m NNO om. Östvänd bergbrant ca 300 m V om Kvarnetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>337203</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6524686</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Östvänd bergvägg vid smal myr  i skog.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Sten, lodyta.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132580383</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97873</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2609</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsfliksmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lejeunea cavifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kilevass, ca 1 km NNO om. Östvänd bergbrant ca 300 m V om Kvarnetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>337226</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6524783</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Östvänd bergvägg i skog.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Sten, lodyta.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132581016</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97873</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2609</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsfliksmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lejeunea cavifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Lindb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kilevass, ca 1 km NNO om. Östvänd bergbrant ca 300 m V om Kvarnetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>337222</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6524732</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Östvänd bergvägg vid smal myr  i skog.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Sten, lodyta.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132581328</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96514</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kilevass, ca 1 km NNO om. Östvänd bergbrant ca 300 m V om Kvarnetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>337222</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6524732</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Östvänd bergvägg vid smal myr  i skog.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sten, lodyta.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132638992</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96514</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kilevass, ca 1 km NNO om. Östvänd bergbrant ca 300 m V om Kvarnetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>337206</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6524696</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Östvänd bergvägg vid smal myr  i skog.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Sten, lodyta.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132638993</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96512</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kilevass, ca 1 km NNO om. Östvänd bergbrant ca 300 m V om Kvarnetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>337206</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6524696</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Östvänd bergvägg vid smal myr  i skog.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Sten, lodyta.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132581018</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96351</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kilevass, ca 1 km NNO om. Östvänd bergbrant ca 300 m V om Kvarnetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>337222</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6524732</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Östvänd bergvägg vid smal myr  i skog.</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Sten, lodyta.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133056788</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96423</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kvarnetjärnet Vut 5, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>337120</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6524546</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell, Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132638989</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96410</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kilevass, ca 950 m NNO om. Östvänd bergbrant ca 300 m V om Kvarnetjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>337203</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6524686</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Östvänd bergvägg vid smal myr  i skog.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Sten, lodyta.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39996-2025 artfynd.xlsx
+++ b/artfynd/A 39996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132638990</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133054808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133056776</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133132832</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1183,6 +1208,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132580383</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132581016</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132581328</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132638992</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132638993</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,6 +1773,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132581018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,6 +1875,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133056788</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1927,8 +1987,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132638989</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>